--- a/examples/HO_SO_CAU_KM19_529/BANG_BOC_TACH_CHI_TIET_TOAN_BO_BAN_VE_CAU_KM19.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/BANG_BOC_TACH_CHI_TIET_TOAN_BO_BAN_VE_CAU_KM19.xlsx
@@ -674,37 +674,31 @@
     <row r="6">
       <c r="B6" s="5">
         <f>'06_MASTER_BOQ_TIEN_LUONG'!G45</f>
-        <v/>
       </c>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="5">
         <f>'06_MASTER_BOQ_TIEN_LUONG'!G46</f>
-        <v/>
       </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="5">
-        <f>'01_DIEN_GIAI_SUPER_T'!J25</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G8</f>
       </c>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="5">
-        <f>'02_DIEN_GIAI_HA_BO'!H39</f>
-        <v/>
+        <f>'02_DIEN_GIAI_HA_BO'!J52</f>
       </c>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
       <c r="N6" s="5">
         <f>'06_MASTER_BOQ_TIEN_LUONG'!G47</f>
-        <v/>
       </c>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="5">
-        <f>'04_DIEN_GIAI_DUONG_TU_NON'!J44</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G34</f>
       </c>
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
@@ -868,20 +862,16 @@
         <v>434.55</v>
       </c>
       <c r="G13" s="13">
-        <f>'01_DIEN_GIAI_SUPER_T'!J24</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G7</f>
       </c>
       <c r="H13" s="13">
         <f>G13-F13</f>
-        <v/>
       </c>
       <c r="I13" s="14">
         <f>IF(F13=0,0,H13/F13)</f>
-        <v/>
       </c>
       <c r="J13" s="15">
         <f>IF(ABS(I13)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -909,20 +899,16 @@
         <v>29911.2</v>
       </c>
       <c r="G14" s="13">
-        <f>'01_DIEN_GIAI_SUPER_T'!J25*1000</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G8*1000</f>
       </c>
       <c r="H14" s="13">
         <f>G14-F14</f>
-        <v/>
       </c>
       <c r="I14" s="14">
         <f>IF(F14=0,0,H14/F14)</f>
-        <v/>
       </c>
       <c r="J14" s="15">
         <f>IF(ABS(I14)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -950,20 +936,16 @@
         <v>89668.81</v>
       </c>
       <c r="G15" s="13">
-        <f>'01_DIEN_GIAI_SUPER_T'!J26*1000</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G9*1000</f>
       </c>
       <c r="H15" s="13">
         <f>G15-F15</f>
-        <v/>
       </c>
       <c r="I15" s="14">
         <f>IF(F15=0,0,H15/F15)</f>
-        <v/>
       </c>
       <c r="J15" s="15">
         <f>IF(ABS(I15)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -991,20 +973,16 @@
         <v>5098.77</v>
       </c>
       <c r="G16" s="13">
-        <f>'01_DIEN_GIAI_SUPER_T'!J27</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G10</f>
       </c>
       <c r="H16" s="13">
         <f>G16-F16</f>
-        <v/>
       </c>
       <c r="I16" s="14">
         <f>IF(F16=0,0,H16/F16)</f>
-        <v/>
       </c>
       <c r="J16" s="15">
         <f>IF(ABS(I16)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="17">
@@ -1032,20 +1010,16 @@
         <v>19.38</v>
       </c>
       <c r="G17" s="13">
-        <f>'01_DIEN_GIAI_SUPER_T'!J35</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G11</f>
       </c>
       <c r="H17" s="13">
         <f>G17-F17</f>
-        <v/>
       </c>
       <c r="I17" s="14">
         <f>IF(F17=0,0,H17/F17)</f>
-        <v/>
       </c>
       <c r="J17" s="15">
         <f>IF(ABS(I17)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="18">
@@ -1073,20 +1047,16 @@
         <v>327.33</v>
       </c>
       <c r="G18" s="13">
-        <f>'01_DIEN_GIAI_SUPER_T'!J43</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G12</f>
       </c>
       <c r="H18" s="13">
         <f>G18-F18</f>
-        <v/>
       </c>
       <c r="I18" s="14">
         <f>IF(F18=0,0,H18/F18)</f>
-        <v/>
       </c>
       <c r="J18" s="15">
         <f>IF(ABS(I18)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="19">
@@ -1114,20 +1084,16 @@
         <v>88357.50999999999</v>
       </c>
       <c r="G19" s="13">
-        <f>'01_DIEN_GIAI_SUPER_T'!J44*1000</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G13*1000</f>
       </c>
       <c r="H19" s="13">
         <f>G19-F19</f>
-        <v/>
       </c>
       <c r="I19" s="14">
         <f>IF(F19=0,0,H19/F19)</f>
-        <v/>
       </c>
       <c r="J19" s="15">
         <f>IF(ABS(I19)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="20">
@@ -1155,20 +1121,16 @@
         <v>13.23</v>
       </c>
       <c r="G20" s="13">
-        <f>'01_DIEN_GIAI_SUPER_T'!J50</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G14</f>
       </c>
       <c r="H20" s="13">
         <f>G20-F20</f>
-        <v/>
       </c>
       <c r="I20" s="14">
         <f>IF(F20=0,0,H20/F20)</f>
-        <v/>
       </c>
       <c r="J20" s="15">
         <f>IF(ABS(I20)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="21">
@@ -1196,20 +1158,16 @@
         <v>1380.39</v>
       </c>
       <c r="G21" s="13">
-        <f>'01_DIEN_GIAI_SUPER_T'!J56</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G15</f>
       </c>
       <c r="H21" s="13">
         <f>G21-F21</f>
-        <v/>
       </c>
       <c r="I21" s="14">
         <f>IF(F21=0,0,H21/F21)</f>
-        <v/>
       </c>
       <c r="J21" s="15">
         <f>IF(ABS(I21)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="22">
@@ -1252,20 +1210,16 @@
         <v>403.75</v>
       </c>
       <c r="G23" s="13">
-        <f>'02_DIEN_GIAI_HA_BO'!J15</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G17</f>
       </c>
       <c r="H23" s="13">
         <f>G23-F23</f>
-        <v/>
       </c>
       <c r="I23" s="14">
         <f>IF(F23=0,0,H23/F23)</f>
-        <v/>
       </c>
       <c r="J23" s="15">
         <f>IF(ABS(I23)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="24">
@@ -1293,20 +1247,16 @@
         <v>40954.12</v>
       </c>
       <c r="G24" s="13">
-        <f>'02_DIEN_GIAI_HA_BO'!J16*1000</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G18*1000</f>
       </c>
       <c r="H24" s="13">
         <f>G24-F24</f>
-        <v/>
       </c>
       <c r="I24" s="14">
         <f>IF(F24=0,0,H24/F24)</f>
-        <v/>
       </c>
       <c r="J24" s="15">
         <f>IF(ABS(I24)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -1334,20 +1284,16 @@
         <v>1015.22</v>
       </c>
       <c r="G25" s="13">
-        <f>'02_DIEN_GIAI_HA_BO'!J28</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G19</f>
       </c>
       <c r="H25" s="13">
         <f>G25-F25</f>
-        <v/>
       </c>
       <c r="I25" s="14">
         <f>IF(F25=0,0,H25/F25)</f>
-        <v/>
       </c>
       <c r="J25" s="15">
         <f>IF(ABS(I25)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="26">
@@ -1375,20 +1321,16 @@
         <v>126127.25</v>
       </c>
       <c r="G26" s="13">
-        <f>'02_DIEN_GIAI_HA_BO'!J29*1000</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G20*1000</f>
       </c>
       <c r="H26" s="13">
         <f>G26-F26</f>
-        <v/>
       </c>
       <c r="I26" s="14">
         <f>IF(F26=0,0,H26/F26)</f>
-        <v/>
       </c>
       <c r="J26" s="15">
         <f>IF(ABS(I26)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="27">
@@ -1416,20 +1358,16 @@
         <v>1006.54</v>
       </c>
       <c r="G27" s="13">
-        <f>'02_DIEN_GIAI_HA_BO'!J38</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G21</f>
       </c>
       <c r="H27" s="13">
         <f>G27-F27</f>
-        <v/>
       </c>
       <c r="I27" s="14">
         <f>IF(F27=0,0,H27/F27)</f>
-        <v/>
       </c>
       <c r="J27" s="15">
         <f>IF(ABS(I27)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="28">
@@ -1457,20 +1395,16 @@
         <v>108884.17</v>
       </c>
       <c r="G28" s="13">
-        <f>'02_DIEN_GIAI_HA_BO'!J40*1000</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G22*1000</f>
       </c>
       <c r="H28" s="13">
         <f>G28-F28</f>
-        <v/>
       </c>
       <c r="I28" s="14">
         <f>IF(F28=0,0,H28/F28)</f>
-        <v/>
       </c>
       <c r="J28" s="15">
         <f>IF(ABS(I28)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="29">
@@ -1513,20 +1447,16 @@
         <v>67.38</v>
       </c>
       <c r="G30" s="13">
-        <f>'03_DIEN_GIAI_PHU_TRO'!J15</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G24</f>
       </c>
       <c r="H30" s="13">
         <f>G30-F30</f>
-        <v/>
       </c>
       <c r="I30" s="14">
         <f>IF(F30=0,0,H30/F30)</f>
-        <v/>
       </c>
       <c r="J30" s="15">
         <f>IF(ABS(I30)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="31">
@@ -1554,20 +1484,16 @@
         <v>104.28</v>
       </c>
       <c r="G31" s="13">
-        <f>'03_DIEN_GIAI_PHU_TRO'!J25</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G25</f>
       </c>
       <c r="H31" s="13">
         <f>G31-F31</f>
-        <v/>
       </c>
       <c r="I31" s="14">
         <f>IF(F31=0,0,H31/F31)</f>
-        <v/>
       </c>
       <c r="J31" s="15">
         <f>IF(ABS(I31)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="32">
@@ -1595,20 +1521,16 @@
         <v>29602.42</v>
       </c>
       <c r="G32" s="13">
-        <f>'03_DIEN_GIAI_PHU_TRO'!J26*1000</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G26*1000</f>
       </c>
       <c r="H32" s="13">
         <f>G32-F32</f>
-        <v/>
       </c>
       <c r="I32" s="14">
         <f>IF(F32=0,0,H32/F32)</f>
-        <v/>
       </c>
       <c r="J32" s="15">
         <f>IF(ABS(I32)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="33">
@@ -1636,20 +1558,16 @@
         <v>30</v>
       </c>
       <c r="G33" s="13">
-        <f>'03_DIEN_GIAI_PHU_TRO'!E34</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G27</f>
       </c>
       <c r="H33" s="13">
         <f>G33-F33</f>
-        <v/>
       </c>
       <c r="I33" s="14">
         <f>IF(F33=0,0,H33/F33)</f>
-        <v/>
       </c>
       <c r="J33" s="15">
         <f>IF(ABS(I33)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="34">
@@ -1677,20 +1595,16 @@
         <v>24.5</v>
       </c>
       <c r="G34" s="13">
-        <f>'03_DIEN_GIAI_PHU_TRO'!F40</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G28</f>
       </c>
       <c r="H34" s="13">
         <f>G34-F34</f>
-        <v/>
       </c>
       <c r="I34" s="14">
         <f>IF(F34=0,0,H34/F34)</f>
-        <v/>
       </c>
       <c r="J34" s="15">
         <f>IF(ABS(I34)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="35">
@@ -1718,20 +1632,16 @@
         <v>24</v>
       </c>
       <c r="G35" s="13">
-        <f>'03_DIEN_GIAI_PHU_TRO'!E48</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G29</f>
       </c>
       <c r="H35" s="13">
         <f>G35-F35</f>
-        <v/>
       </c>
       <c r="I35" s="14">
         <f>IF(F35=0,0,H35/F35)</f>
-        <v/>
       </c>
       <c r="J35" s="15">
         <f>IF(ABS(I35)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="36">
@@ -1774,20 +1684,16 @@
         <v>104.74</v>
       </c>
       <c r="G37" s="13">
-        <f>'04_DIEN_GIAI_DUONG_TU_NON'!J10</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G31</f>
       </c>
       <c r="H37" s="13">
         <f>G37-F37</f>
-        <v/>
       </c>
       <c r="I37" s="14">
         <f>IF(F37=0,0,H37/F37)</f>
-        <v/>
       </c>
       <c r="J37" s="15">
         <f>IF(ABS(I37)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="38">
@@ -1815,20 +1721,16 @@
         <v>115.88</v>
       </c>
       <c r="G38" s="13">
-        <f>'04_DIEN_GIAI_DUONG_TU_NON'!J16</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G32</f>
       </c>
       <c r="H38" s="13">
         <f>G38-F38</f>
-        <v/>
       </c>
       <c r="I38" s="14">
         <f>IF(F38=0,0,H38/F38)</f>
-        <v/>
       </c>
       <c r="J38" s="15">
         <f>IF(ABS(I38)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="39">
@@ -1856,20 +1758,16 @@
         <v>387.97</v>
       </c>
       <c r="G39" s="13">
-        <f>'04_DIEN_GIAI_DUONG_TU_NON'!J30</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G33</f>
       </c>
       <c r="H39" s="13">
         <f>G39-F39</f>
-        <v/>
       </c>
       <c r="I39" s="14">
         <f>IF(F39=0,0,H39/F39)</f>
-        <v/>
       </c>
       <c r="J39" s="15">
         <f>IF(ABS(I39)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
     <row r="40">
@@ -1897,20 +1795,16 @@
         <v>1012.96</v>
       </c>
       <c r="G40" s="13">
-        <f>'04_DIEN_GIAI_DUONG_TU_NON'!J44</f>
-        <v/>
+        <f>'06_MASTER_BOQ_TIEN_LUONG'!G34</f>
       </c>
       <c r="H40" s="13">
         <f>G40-F40</f>
-        <v/>
       </c>
       <c r="I40" s="14">
         <f>IF(F40=0,0,H40/F40)</f>
-        <v/>
       </c>
       <c r="J40" s="15">
         <f>IF(ABS(I40)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -5323,7 +5217,6 @@
       </c>
       <c r="K7" s="13">
         <f>ROUND(F7*G7*H7*I7*J7, 3)</f>
-        <v/>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
@@ -5365,7 +5258,6 @@
       </c>
       <c r="K8" s="13">
         <f>ROUND(F8*G8*H8*I8*J8, 3)</f>
-        <v/>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
@@ -5407,7 +5299,6 @@
       </c>
       <c r="K9" s="13">
         <f>ROUND(F9*G9*H9*I9*J9, 3)</f>
-        <v/>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
@@ -5449,7 +5340,6 @@
       </c>
       <c r="K10" s="13">
         <f>ROUND(F10*G10*H10*I10*J10, 3)</f>
-        <v/>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
@@ -5491,7 +5381,6 @@
       </c>
       <c r="K11" s="13">
         <f>ROUND(F11*G11*H11*I11*J11, 3)</f>
-        <v/>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
@@ -5533,7 +5422,6 @@
       </c>
       <c r="K12" s="13">
         <f>ROUND(F12*G12*H12*I12*J12, 3)</f>
-        <v/>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
@@ -5575,7 +5463,6 @@
       </c>
       <c r="K13" s="13">
         <f>ROUND(F13*G13*H13*I13*J13, 3)</f>
-        <v/>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
@@ -5617,7 +5504,6 @@
       </c>
       <c r="K14" s="13">
         <f>ROUND(F14*G14*H14*I14*J14, 3)</f>
-        <v/>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
@@ -5659,7 +5545,6 @@
       </c>
       <c r="K15" s="13">
         <f>ROUND(F15*G15, 3)</f>
-        <v/>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
@@ -5701,7 +5586,6 @@
       </c>
       <c r="K16" s="13">
         <f>ROUND(F16*G16, 2)</f>
-        <v/>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
@@ -5725,7 +5609,6 @@
       <c r="J17" s="17" t="n"/>
       <c r="K17" s="19">
         <f>SUM(K7:K8)+SUM(K11:K12)</f>
-        <v/>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
@@ -5784,7 +5667,6 @@
       </c>
       <c r="K19" s="13">
         <f>ROUND(F19*G19*H19*I19*J19, 3)</f>
-        <v/>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
@@ -5826,7 +5708,6 @@
       </c>
       <c r="K20" s="13">
         <f>ROUND(F20*G20*J20, 3)</f>
-        <v/>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
@@ -5868,7 +5749,6 @@
       </c>
       <c r="K21" s="13">
         <f>ROUND(F21*G21*H21*I21*J21, 3)</f>
-        <v/>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
@@ -5910,7 +5790,6 @@
       </c>
       <c r="K22" s="13">
         <f>ROUND(F22*G22*H22*I22*J22, 3)</f>
-        <v/>
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
@@ -5952,7 +5831,6 @@
       </c>
       <c r="K23" s="13">
         <f>ROUND(F23*G23*H23*I23*J23, 3)</f>
-        <v/>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
@@ -5994,7 +5872,6 @@
       </c>
       <c r="K24" s="13">
         <f>ROUND(F24*G24*J24, 3)</f>
-        <v/>
       </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
@@ -6036,7 +5913,6 @@
       </c>
       <c r="K25" s="13">
         <f>ROUND(F25*G25*H25*I25*J25, 3)</f>
-        <v/>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
@@ -6078,7 +5954,6 @@
       </c>
       <c r="K26" s="13">
         <f>ROUND(F26*G26*H26*I26*J26, 3)</f>
-        <v/>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
@@ -6120,7 +5995,6 @@
       </c>
       <c r="K27" s="13">
         <f>ROUND(F27*G27, 3)</f>
-        <v/>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
@@ -6162,7 +6036,6 @@
       </c>
       <c r="K28" s="13">
         <f>ROUND(F28*G28, 2)</f>
-        <v/>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
@@ -6186,7 +6059,6 @@
       <c r="J29" s="17" t="n"/>
       <c r="K29" s="19">
         <f>SUM(K19:K21)+SUM(K23:K25)</f>
-        <v/>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
@@ -6245,7 +6117,6 @@
       </c>
       <c r="K31" s="13">
         <f>ROUND(F31*G31, 1)</f>
-        <v/>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
@@ -6287,7 +6158,6 @@
       </c>
       <c r="K32" s="13">
         <f>ROUND(F32*G32, 1)</f>
-        <v/>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
@@ -6329,7 +6199,6 @@
       </c>
       <c r="K33" s="13">
         <f>ROUND(F33*G33, 1)</f>
-        <v/>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
@@ -6371,7 +6240,6 @@
       </c>
       <c r="K34" s="13">
         <f>ROUND(F34*G34, 1)</f>
-        <v/>
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
@@ -6413,7 +6281,6 @@
       </c>
       <c r="K35" s="13">
         <f>ROUND(F35*G35*H35*I35*J35, 3)</f>
-        <v/>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
@@ -6455,7 +6322,6 @@
       </c>
       <c r="K36" s="13">
         <f>ROUND(F36*G36*H36*I36*J36, 3)</f>
-        <v/>
       </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
@@ -6497,7 +6363,6 @@
       </c>
       <c r="K37" s="13">
         <f>ROUND(F37*G37*H37*I37*J37, 3)</f>
-        <v/>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
@@ -6539,7 +6404,6 @@
       </c>
       <c r="K38" s="13">
         <f>ROUND(F38*G38*H38*I38*J38, 3)</f>
-        <v/>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
@@ -6581,7 +6445,6 @@
       </c>
       <c r="K39" s="13">
         <f>ROUND(F39*G39*H39*I39*J39, 3)</f>
-        <v/>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
@@ -6623,7 +6486,6 @@
       </c>
       <c r="K40" s="13">
         <f>ROUND(F40*G40, 2)</f>
-        <v/>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
@@ -6665,7 +6527,6 @@
       </c>
       <c r="K41" s="13">
         <f>ROUND(F41*G41, 3)</f>
-        <v/>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
@@ -6707,7 +6568,6 @@
       </c>
       <c r="K42" s="13">
         <f>ROUND(F42*G42, 1)</f>
-        <v/>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
@@ -6749,7 +6609,6 @@
       </c>
       <c r="K43" s="13">
         <f>ROUND(F43*G43, 1)</f>
-        <v/>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
@@ -6791,7 +6650,6 @@
       </c>
       <c r="K44" s="13">
         <f>ROUND(F44*G44, 0)</f>
-        <v/>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
@@ -6815,7 +6673,6 @@
       <c r="J45" s="17" t="n"/>
       <c r="K45" s="19">
         <f>SUM(K31:K34)</f>
-        <v/>
       </c>
       <c r="L45" s="20" t="inlineStr">
         <is>
@@ -6839,7 +6696,6 @@
       <c r="J46" s="17" t="n"/>
       <c r="K46" s="19">
         <f>SUM(K35:K38)</f>
-        <v/>
       </c>
       <c r="L46" s="20" t="inlineStr">
         <is>
@@ -6856,7 +6712,6 @@
       </c>
       <c r="J48" s="22">
         <f>K17</f>
-        <v/>
       </c>
     </row>
     <row r="49">
@@ -6867,7 +6722,6 @@
       </c>
       <c r="J49" s="22">
         <f>K15</f>
-        <v/>
       </c>
     </row>
     <row r="50">
@@ -6877,8 +6731,7 @@
         </is>
       </c>
       <c r="J50" s="22">
-        <f>K30</f>
-        <v/>
+        <f>K29</f>
       </c>
     </row>
     <row r="51">
@@ -6888,8 +6741,7 @@
         </is>
       </c>
       <c r="J51" s="22">
-        <f>K29</f>
-        <v/>
+        <f>K27</f>
       </c>
     </row>
     <row r="52">
@@ -6899,8 +6751,7 @@
         </is>
       </c>
       <c r="J52" s="22">
-        <f>K46</f>
-        <v/>
+        <f>K45</f>
       </c>
     </row>
     <row r="53">
@@ -6910,8 +6761,7 @@
         </is>
       </c>
       <c r="J53" s="22">
-        <f>K47</f>
-        <v/>
+        <f>K46</f>
       </c>
     </row>
     <row r="54">
@@ -6922,7 +6772,6 @@
       </c>
       <c r="J54" s="22">
         <f>K41</f>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -7086,7 +6935,6 @@
       </c>
       <c r="K7" s="13">
         <f>ROUND(F7*G7*H7*I7*J7, 3)</f>
-        <v/>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
@@ -7128,7 +6976,6 @@
       </c>
       <c r="K8" s="13">
         <f>ROUND(F8*G8*H8*I8*J8, 3)</f>
-        <v/>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
@@ -7170,7 +7017,6 @@
       </c>
       <c r="K9" s="13">
         <f>ROUND(F9*G9, 2)</f>
-        <v/>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
@@ -7212,7 +7058,6 @@
       </c>
       <c r="K10" s="13">
         <f>ROUND(F10*G10, 2)</f>
-        <v/>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
@@ -7254,7 +7099,6 @@
       </c>
       <c r="K11" s="13">
         <f>ROUND(F11*G11*H11*I11*J11, 3)</f>
-        <v/>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
@@ -7296,7 +7140,6 @@
       </c>
       <c r="K12" s="13">
         <f>ROUND(F12*G12*H12*I12*J12, 3)</f>
-        <v/>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
@@ -7338,7 +7181,6 @@
       </c>
       <c r="K13" s="13">
         <f>ROUND(F13*G13, 2)</f>
-        <v/>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
@@ -7380,7 +7222,6 @@
       </c>
       <c r="K14" s="13">
         <f>ROUND(F14*G14, 2)</f>
-        <v/>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
@@ -7404,7 +7245,6 @@
       <c r="J15" s="17" t="n"/>
       <c r="K15" s="19">
         <f>K7+K11</f>
-        <v/>
       </c>
       <c r="L15" s="20" t="inlineStr">
         <is>
@@ -7462,8 +7302,7 @@
         <v>0.547</v>
       </c>
       <c r="K17" s="13">
-        <f>ROUND(F18*G18*J18, 3)</f>
-        <v/>
+        <f>ROUND(F17*G17*J17, 3)</f>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
@@ -7504,8 +7343,7 @@
         <v>0.55</v>
       </c>
       <c r="K18" s="13">
-        <f>ROUND(F19*G19*J19, 3)</f>
-        <v/>
+        <f>ROUND(F18*G18*J18, 3)</f>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
@@ -7546,8 +7384,7 @@
         <v>0.349</v>
       </c>
       <c r="K19" s="13">
-        <f>ROUND(F20*G20*J20, 3)</f>
-        <v/>
+        <f>ROUND(F19*G19*J19, 3)</f>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
@@ -7588,8 +7425,7 @@
         <v>0.351</v>
       </c>
       <c r="K20" s="13">
-        <f>ROUND(F21*G21*J21, 3)</f>
-        <v/>
+        <f>ROUND(F20*G20*J20, 3)</f>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
@@ -7630,8 +7466,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="13">
-        <f>ROUND(F22*G22, 2)</f>
-        <v/>
+        <f>ROUND(F21*G21, 2)</f>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
@@ -7672,8 +7507,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="13">
-        <f>ROUND(F23*G23, 2)</f>
-        <v/>
+        <f>ROUND(F22*G22, 2)</f>
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
@@ -7714,8 +7548,7 @@
         <v>1</v>
       </c>
       <c r="K23" s="13">
-        <f>ROUND(F24*G24, 1)</f>
-        <v/>
+        <f>ROUND(F23*G23, 1)</f>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
@@ -7738,8 +7571,7 @@
       <c r="I24" s="17" t="n"/>
       <c r="J24" s="17" t="n"/>
       <c r="K24" s="19">
-        <f>SUM(K18:K21)</f>
-        <v/>
+        <f>SUM(K17:K20)</f>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
@@ -7797,8 +7629,7 @@
         <v>1</v>
       </c>
       <c r="K26" s="13">
-        <f>ROUND(F27*G27, 2)</f>
-        <v/>
+        <f>ROUND(F26*G26, 2)</f>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
@@ -7839,8 +7670,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="13">
-        <f>ROUND(F28*G28, 2)</f>
-        <v/>
+        <f>ROUND(F27*G27, 2)</f>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
@@ -7881,8 +7711,7 @@
         <v>1</v>
       </c>
       <c r="K28" s="13">
-        <f>ROUND(F29*G29, 2)</f>
-        <v/>
+        <f>ROUND(F28*G28, 2)</f>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
@@ -7905,8 +7734,7 @@
       <c r="I29" s="17" t="n"/>
       <c r="J29" s="17" t="n"/>
       <c r="K29" s="19">
-        <f>SUM(K27:K29)</f>
-        <v/>
+        <f>SUM(K26:K28)</f>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
@@ -7964,8 +7792,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="13">
-        <f>ROUND(F32, 0)</f>
-        <v/>
+        <f>ROUND(F31, 0)</f>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
@@ -8006,8 +7833,7 @@
         <v>1</v>
       </c>
       <c r="K32" s="13">
-        <f>ROUND(F33, 0)</f>
-        <v/>
+        <f>ROUND(F32, 0)</f>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
@@ -8048,8 +7874,7 @@
         <v>1</v>
       </c>
       <c r="K33" s="13">
-        <f>ROUND(F34*G34, 2)</f>
-        <v/>
+        <f>ROUND(F33*G33, 2)</f>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
@@ -8090,8 +7915,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="13">
-        <f>ROUND(F35*G35, 0)</f>
-        <v/>
+        <f>ROUND(F34*G34, 0)</f>
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
@@ -8132,8 +7956,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="13">
-        <f>ROUND(F36*G36, 3)</f>
-        <v/>
+        <f>ROUND(F35*G35, 3)</f>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
@@ -8156,8 +7979,7 @@
       <c r="I36" s="17" t="n"/>
       <c r="J36" s="17" t="n"/>
       <c r="K36" s="19">
-        <f>K32+K33</f>
-        <v/>
+        <f>K31+K32</f>
       </c>
       <c r="L36" s="20" t="inlineStr">
         <is>
@@ -8215,8 +8037,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="13">
-        <f>ROUND(F39*G39, 2)</f>
-        <v/>
+        <f>ROUND(F38*G38, 2)</f>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
@@ -8257,8 +8078,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="13">
-        <f>ROUND(F40*G40*H40*I40*J40, 3)</f>
-        <v/>
+        <f>ROUND(F39*G39*H39*I39*J39, 3)</f>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
@@ -8299,8 +8119,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="13">
-        <f>ROUND(F41*G41, 2)</f>
-        <v/>
+        <f>ROUND(F40*G40, 2)</f>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
@@ -8341,8 +8160,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="13">
-        <f>ROUND(F42*G42, 2)</f>
-        <v/>
+        <f>ROUND(F41*G41, 2)</f>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
@@ -8383,8 +8201,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="13">
-        <f>ROUND(F43*G43, 0)</f>
-        <v/>
+        <f>ROUND(F42*G42, 0)</f>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
@@ -8407,8 +8224,7 @@
       <c r="I43" s="17" t="n"/>
       <c r="J43" s="17" t="n"/>
       <c r="K43" s="19">
-        <f>K39</f>
-        <v/>
+        <f>K38</f>
       </c>
       <c r="L43" s="20" t="inlineStr">
         <is>
@@ -8466,8 +8282,7 @@
         <v>1</v>
       </c>
       <c r="K45" s="13">
-        <f>ROUND(F46*G46, 2)</f>
-        <v/>
+        <f>ROUND(F45*G45, 2)</f>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
@@ -8508,8 +8323,7 @@
         <v>1</v>
       </c>
       <c r="K46" s="13">
-        <f>ROUND(F47*G47, 2)</f>
-        <v/>
+        <f>ROUND(F46*G46, 2)</f>
       </c>
       <c r="L46" s="12" t="inlineStr">
         <is>
@@ -8550,8 +8364,7 @@
         <v>1</v>
       </c>
       <c r="K47" s="13">
-        <f>ROUND(F48, 0)</f>
-        <v/>
+        <f>ROUND(F47, 0)</f>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
@@ -8592,8 +8405,7 @@
         <v>1</v>
       </c>
       <c r="K48" s="13">
-        <f>ROUND(F49*G49, 2)</f>
-        <v/>
+        <f>ROUND(F48*G48, 2)</f>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
@@ -8634,8 +8446,7 @@
         <v>1</v>
       </c>
       <c r="K49" s="13">
-        <f>ROUND(F50*G50, 2)</f>
-        <v/>
+        <f>ROUND(F49*G49, 2)</f>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
@@ -8676,8 +8487,7 @@
         <v>1</v>
       </c>
       <c r="K50" s="13">
-        <f>ROUND(F51*G51, 0)</f>
-        <v/>
+        <f>ROUND(F50*G50, 0)</f>
       </c>
       <c r="L50" s="12" t="inlineStr">
         <is>
@@ -8700,8 +8510,7 @@
       <c r="I51" s="17" t="n"/>
       <c r="J51" s="17" t="n"/>
       <c r="K51" s="19">
-        <f>K46/16.55</f>
-        <v/>
+        <f>F45</f>
       </c>
       <c r="L51" s="20" t="inlineStr">
         <is>
@@ -8718,7 +8527,6 @@
       </c>
       <c r="J53" s="22">
         <f>K15</f>
-        <v/>
       </c>
     </row>
     <row r="54">
@@ -8728,8 +8536,7 @@
         </is>
       </c>
       <c r="J54" s="22">
-        <f>K25</f>
-        <v/>
+        <f>K24</f>
       </c>
     </row>
     <row r="55">
@@ -8739,8 +8546,7 @@
         </is>
       </c>
       <c r="J55" s="22">
-        <f>(K9+K13+K22)/1000</f>
-        <v/>
+        <f>(K9+K13+K21)/1000</f>
       </c>
     </row>
     <row r="56">
@@ -8750,8 +8556,7 @@
         </is>
       </c>
       <c r="J56" s="22">
-        <f>K37</f>
-        <v/>
+        <f>K36</f>
       </c>
     </row>
     <row r="57">
@@ -8761,8 +8566,7 @@
         </is>
       </c>
       <c r="J57" s="22">
-        <f>K44</f>
-        <v/>
+        <f>K43</f>
       </c>
     </row>
     <row r="58">
@@ -8772,8 +8576,7 @@
         </is>
       </c>
       <c r="J58" s="22">
-        <f>K52</f>
-        <v/>
+        <f>K51</f>
       </c>
     </row>
   </sheetData>
@@ -11267,7 +11070,6 @@
       </c>
       <c r="G7" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K11</f>
-        <v/>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
@@ -11303,7 +11105,6 @@
       </c>
       <c r="G8" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K16</f>
-        <v/>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
@@ -11339,7 +11140,6 @@
       </c>
       <c r="G9" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K21</f>
-        <v/>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
@@ -11375,7 +11175,6 @@
       </c>
       <c r="G10" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K27</f>
-        <v/>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
@@ -11411,7 +11210,6 @@
       </c>
       <c r="G11" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K34</f>
-        <v/>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
@@ -11447,7 +11245,6 @@
       </c>
       <c r="G12" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K43</f>
-        <v/>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
@@ -11483,7 +11280,6 @@
       </c>
       <c r="G13" s="13">
         <f>('01_DIEN_GIAI_SUPER_T'!K31+'01_DIEN_GIAI_SUPER_T'!K41)/1000</f>
-        <v/>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
@@ -11519,7 +11315,6 @@
       </c>
       <c r="G14" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K48</f>
-        <v/>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
@@ -11555,7 +11350,6 @@
       </c>
       <c r="G15" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K53</f>
-        <v/>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
@@ -11604,7 +11398,6 @@
       </c>
       <c r="G17" s="13">
         <f>'02_DIEN_GIAI_HA_BO'!K17</f>
-        <v/>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
@@ -11640,7 +11433,6 @@
       </c>
       <c r="G18" s="13">
         <f>'02_DIEN_GIAI_HA_BO'!K15</f>
-        <v/>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
@@ -11675,8 +11467,7 @@
         </is>
       </c>
       <c r="G19" s="13">
-        <f>'02_DIEN_GIAI_HA_BO'!K30</f>
-        <v/>
+        <f>'02_DIEN_GIAI_HA_BO'!K29</f>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
@@ -11711,8 +11502,7 @@
         </is>
       </c>
       <c r="G20" s="13">
-        <f>'02_DIEN_GIAI_HA_BO'!K29</f>
-        <v/>
+        <f>'02_DIEN_GIAI_HA_BO'!K27</f>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
@@ -11747,8 +11537,7 @@
         </is>
       </c>
       <c r="G21" s="13">
-        <f>'02_DIEN_GIAI_HA_BO'!K47</f>
-        <v/>
+        <f>'02_DIEN_GIAI_HA_BO'!K46</f>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
@@ -11784,7 +11573,6 @@
       </c>
       <c r="G22" s="13">
         <f>'02_DIEN_GIAI_HA_BO'!K41</f>
-        <v/>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
@@ -11833,7 +11621,6 @@
       </c>
       <c r="G24" s="13">
         <f>'03_DIEN_GIAI_PHU_TRO'!K15</f>
-        <v/>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
@@ -11868,8 +11655,7 @@
         </is>
       </c>
       <c r="G25" s="13">
-        <f>'03_DIEN_GIAI_PHU_TRO'!K25</f>
-        <v/>
+        <f>'03_DIEN_GIAI_PHU_TRO'!K24</f>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
@@ -11904,8 +11690,7 @@
         </is>
       </c>
       <c r="G26" s="13">
-        <f>('03_DIEN_GIAI_PHU_TRO'!K9+'03_DIEN_GIAI_PHU_TRO'!K13+'03_DIEN_GIAI_PHU_TRO'!K22)/1000</f>
-        <v/>
+        <f>('03_DIEN_GIAI_PHU_TRO'!K9+'03_DIEN_GIAI_PHU_TRO'!K13+'03_DIEN_GIAI_PHU_TRO'!K21)/1000</f>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
@@ -11940,8 +11725,7 @@
         </is>
       </c>
       <c r="G27" s="13">
-        <f>'03_DIEN_GIAI_PHU_TRO'!K37</f>
-        <v/>
+        <f>'03_DIEN_GIAI_PHU_TRO'!K36</f>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
@@ -11976,8 +11760,7 @@
         </is>
       </c>
       <c r="G28" s="13">
-        <f>'03_DIEN_GIAI_PHU_TRO'!K44</f>
-        <v/>
+        <f>'03_DIEN_GIAI_PHU_TRO'!K43</f>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
@@ -12012,8 +11795,7 @@
         </is>
       </c>
       <c r="G29" s="13">
-        <f>'03_DIEN_GIAI_PHU_TRO'!K52</f>
-        <v/>
+        <f>'03_DIEN_GIAI_PHU_TRO'!K51</f>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
@@ -12062,7 +11844,6 @@
       </c>
       <c r="G31" s="13">
         <f>'04_DIEN_GIAI_DUONG_TU_NON'!K11</f>
-        <v/>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
@@ -12098,7 +11879,6 @@
       </c>
       <c r="G32" s="13">
         <f>'04_DIEN_GIAI_DUONG_TU_NON'!K19</f>
-        <v/>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
@@ -12134,7 +11914,6 @@
       </c>
       <c r="G33" s="13">
         <f>'04_DIEN_GIAI_DUONG_TU_NON'!K30</f>
-        <v/>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
@@ -12170,7 +11949,6 @@
       </c>
       <c r="G34" s="13">
         <f>'04_DIEN_GIAI_DUONG_TU_NON'!K34</f>
-        <v/>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
@@ -12254,7 +12032,6 @@
       </c>
       <c r="G37" s="13">
         <f>'05_DIEN_GIAI_BPTC_CON'!K21</f>
-        <v/>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
@@ -12290,7 +12067,6 @@
       </c>
       <c r="G38" s="13">
         <f>'05_DIEN_GIAI_BPTC_CON'!K28</f>
-        <v/>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
@@ -12312,7 +12088,6 @@
       </c>
       <c r="G45" s="24">
         <f>G7+G11+G12+G14+G17+G19+G21+G24+G25+G32</f>
-        <v/>
       </c>
     </row>
     <row r="46">
@@ -12323,7 +12098,6 @@
       </c>
       <c r="G46" s="24">
         <f>G9+G13+G18+G20+G22+G26</f>
-        <v/>
       </c>
     </row>
     <row r="47">
@@ -12333,8 +12107,7 @@
         </is>
       </c>
       <c r="G47" s="24">
-        <f>G10+'02_DIEN_GIAI_HA_BO'!K16+'02_DIEN_GIAI_HA_BO'!K28+'03_DIEN_GIAI_PHU_TRO'!K10+'03_DIEN_GIAI_PHU_TRO'!K14+'03_DIEN_GIAI_PHU_TRO'!K23+'04_DIEN_GIAI_DUONG_TU_NON'!K14</f>
-        <v/>
+        <f>G10+'02_DIEN_GIAI_HA_BO'!K16+'02_DIEN_GIAI_HA_BO'!K28+'03_DIEN_GIAI_PHU_TRO'!K10+'03_DIEN_GIAI_PHU_TRO'!K14+'03_DIEN_GIAI_PHU_TRO'!K22+'04_DIEN_GIAI_DUONG_TU_NON'!K14</f>
       </c>
     </row>
   </sheetData>
